--- a/data/Prevencion_de_violencia_de_genero_CAVV/SAFEkits.xlsx
+++ b/data/Prevencion_de_violencia_de_genero_CAVV/SAFEkits.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Prevencion_de_violencia_de_genero_CAVV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05399FCC-6F27-4939-915F-4263159D717E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F7677C-40B5-4B35-BC20-A0BF885B6800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9984" yWindow="1164" windowWidth="11424" windowHeight="9420" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen" sheetId="1" r:id="rId1"/>
@@ -1317,6 +1317,84 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1326,115 +1404,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1476,90 +1453,6 @@
     <dxf>
       <font>
         <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -1624,12 +1517,119 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
       <border outline="0">
         <top style="medium">
           <color indexed="64"/>
         </top>
         <bottom style="thin">
           <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
@@ -1647,22 +1647,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A54:B63" totalsRowShown="0" headerRowBorderDxfId="4" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A54:B63" totalsRowShown="0" headerRowBorderDxfId="9" tableBorderDxfId="8">
   <autoFilter ref="A54:B63" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Año" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Total con querella" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Año" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Total con querella" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="I54:J63" totalsRowShown="0" headerRowDxfId="0" dataDxfId="8" headerRowBorderDxfId="1" tableBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="I54:J63" totalsRowShown="0" headerRowDxfId="5" dataDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="2">
   <autoFilter ref="I54:J63" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Año" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Total sin querella" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Año" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Total sin querella" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1998,37 +1998,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
     </row>
     <row r="3" spans="1:13" ht="21" x14ac:dyDescent="0.4">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="I3" s="80" t="s">
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="I3" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
+      <c r="J3" s="86"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="86"/>
+      <c r="M3" s="86"/>
     </row>
     <row r="4" spans="1:13" ht="31.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="24" t="s">
@@ -2063,7 +2063,7 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="88">
+      <c r="A5" s="93">
         <v>2019</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -2078,7 +2078,7 @@
       <c r="E5" s="3">
         <v>14</v>
       </c>
-      <c r="I5" s="70">
+      <c r="I5" s="96">
         <v>2019</v>
       </c>
       <c r="J5" s="3" t="s">
@@ -2095,7 +2095,7 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="89"/>
+      <c r="A6" s="94"/>
       <c r="B6" s="7" t="s">
         <v>8</v>
       </c>
@@ -2108,7 +2108,7 @@
       <c r="E6" s="7">
         <v>13</v>
       </c>
-      <c r="I6" s="71"/>
+      <c r="I6" s="97"/>
       <c r="J6" s="7" t="s">
         <v>8</v>
       </c>
@@ -2123,7 +2123,7 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="89"/>
+      <c r="A7" s="94"/>
       <c r="B7" s="5" t="s">
         <v>10</v>
       </c>
@@ -2136,7 +2136,7 @@
       <c r="E7" s="5">
         <v>10</v>
       </c>
-      <c r="I7" s="71"/>
+      <c r="I7" s="97"/>
       <c r="J7" s="5" t="s">
         <v>10</v>
       </c>
@@ -2151,7 +2151,7 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="89"/>
+      <c r="A8" s="94"/>
       <c r="B8" s="7" t="s">
         <v>12</v>
       </c>
@@ -2164,7 +2164,7 @@
       <c r="E8" s="7">
         <v>9</v>
       </c>
-      <c r="I8" s="71"/>
+      <c r="I8" s="97"/>
       <c r="J8" s="7" t="s">
         <v>12</v>
       </c>
@@ -2179,7 +2179,7 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="89"/>
+      <c r="A9" s="94"/>
       <c r="B9" s="5" t="s">
         <v>14</v>
       </c>
@@ -2192,7 +2192,7 @@
       <c r="E9" s="5">
         <v>11</v>
       </c>
-      <c r="I9" s="71"/>
+      <c r="I9" s="97"/>
       <c r="J9" s="5" t="s">
         <v>14</v>
       </c>
@@ -2207,7 +2207,7 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="90"/>
+      <c r="A10" s="95"/>
       <c r="B10" s="10" t="s">
         <v>16</v>
       </c>
@@ -2220,7 +2220,7 @@
       <c r="E10" s="10">
         <v>14</v>
       </c>
-      <c r="I10" s="72"/>
+      <c r="I10" s="98"/>
       <c r="J10" s="10" t="s">
         <v>16</v>
       </c>
@@ -2235,7 +2235,7 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="88">
+      <c r="A11" s="93">
         <v>2020</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -2250,7 +2250,7 @@
       <c r="E11" s="3">
         <v>5</v>
       </c>
-      <c r="I11" s="70">
+      <c r="I11" s="96">
         <v>2020</v>
       </c>
       <c r="J11" s="61" t="s">
@@ -2267,7 +2267,7 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="89"/>
+      <c r="A12" s="94"/>
       <c r="B12" s="7" t="s">
         <v>8</v>
       </c>
@@ -2280,7 +2280,7 @@
       <c r="E12" s="7">
         <v>13</v>
       </c>
-      <c r="I12" s="71"/>
+      <c r="I12" s="97"/>
       <c r="J12" s="7" t="s">
         <v>8</v>
       </c>
@@ -2295,7 +2295,7 @@
       </c>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="89"/>
+      <c r="A13" s="94"/>
       <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
@@ -2308,7 +2308,7 @@
       <c r="E13" s="5">
         <v>14</v>
       </c>
-      <c r="I13" s="71"/>
+      <c r="I13" s="97"/>
       <c r="J13" s="5" t="s">
         <v>10</v>
       </c>
@@ -2323,7 +2323,7 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="89"/>
+      <c r="A14" s="94"/>
       <c r="B14" s="7" t="s">
         <v>12</v>
       </c>
@@ -2336,7 +2336,7 @@
       <c r="E14" s="7">
         <v>19</v>
       </c>
-      <c r="I14" s="71"/>
+      <c r="I14" s="97"/>
       <c r="J14" s="7" t="s">
         <v>12</v>
       </c>
@@ -2351,7 +2351,7 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="89"/>
+      <c r="A15" s="94"/>
       <c r="B15" s="5" t="s">
         <v>14</v>
       </c>
@@ -2364,7 +2364,7 @@
       <c r="E15" s="5">
         <v>9</v>
       </c>
-      <c r="I15" s="71"/>
+      <c r="I15" s="97"/>
       <c r="J15" s="5" t="s">
         <v>14</v>
       </c>
@@ -2379,7 +2379,7 @@
       </c>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="90"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="10" t="s">
         <v>16</v>
       </c>
@@ -2392,7 +2392,7 @@
       <c r="E16" s="10">
         <v>9</v>
       </c>
-      <c r="I16" s="72"/>
+      <c r="I16" s="98"/>
       <c r="J16" s="10" t="s">
         <v>16</v>
       </c>
@@ -2407,7 +2407,7 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="86">
+      <c r="A17" s="79">
         <v>2021</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -2422,7 +2422,7 @@
       <c r="E17" s="42">
         <v>15</v>
       </c>
-      <c r="I17" s="82">
+      <c r="I17" s="90">
         <v>2021</v>
       </c>
       <c r="J17" s="3" t="s">
@@ -2439,7 +2439,7 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="83"/>
+      <c r="A18" s="80"/>
       <c r="B18" s="7" t="s">
         <v>8</v>
       </c>
@@ -2452,7 +2452,7 @@
       <c r="E18" s="43">
         <v>13</v>
       </c>
-      <c r="I18" s="77"/>
+      <c r="I18" s="88"/>
       <c r="J18" s="7" t="s">
         <v>8</v>
       </c>
@@ -2467,7 +2467,7 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="83"/>
+      <c r="A19" s="80"/>
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
@@ -2480,7 +2480,7 @@
       <c r="E19" s="44">
         <v>7</v>
       </c>
-      <c r="I19" s="77"/>
+      <c r="I19" s="88"/>
       <c r="J19" s="5" t="s">
         <v>10</v>
       </c>
@@ -2495,7 +2495,7 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="83"/>
+      <c r="A20" s="80"/>
       <c r="B20" s="7" t="s">
         <v>12</v>
       </c>
@@ -2508,7 +2508,7 @@
       <c r="E20" s="43">
         <v>9</v>
       </c>
-      <c r="I20" s="77"/>
+      <c r="I20" s="88"/>
       <c r="J20" s="7" t="s">
         <v>12</v>
       </c>
@@ -2523,7 +2523,7 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="83"/>
+      <c r="A21" s="80"/>
       <c r="B21" s="5" t="s">
         <v>14</v>
       </c>
@@ -2536,7 +2536,7 @@
       <c r="E21" s="44">
         <v>10</v>
       </c>
-      <c r="I21" s="77"/>
+      <c r="I21" s="88"/>
       <c r="J21" s="5" t="s">
         <v>14</v>
       </c>
@@ -2551,7 +2551,7 @@
       </c>
     </row>
     <row r="22" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="87"/>
+      <c r="A22" s="92"/>
       <c r="B22" s="10" t="s">
         <v>16</v>
       </c>
@@ -2564,7 +2564,7 @@
       <c r="E22" s="45">
         <v>8</v>
       </c>
-      <c r="I22" s="81"/>
+      <c r="I22" s="89"/>
       <c r="J22" s="10" t="s">
         <v>16</v>
       </c>
@@ -2579,7 +2579,7 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="85">
+      <c r="A23" s="91">
         <v>2022</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -2594,7 +2594,7 @@
       <c r="E23" s="42">
         <v>7</v>
       </c>
-      <c r="I23" s="76">
+      <c r="I23" s="87">
         <v>2022</v>
       </c>
       <c r="J23" s="3" t="s">
@@ -2611,7 +2611,7 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="83"/>
+      <c r="A24" s="80"/>
       <c r="B24" s="7" t="s">
         <v>8</v>
       </c>
@@ -2624,7 +2624,7 @@
       <c r="E24" s="43">
         <v>17</v>
       </c>
-      <c r="I24" s="77"/>
+      <c r="I24" s="88"/>
       <c r="J24" s="7" t="s">
         <v>8</v>
       </c>
@@ -2639,7 +2639,7 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" s="83"/>
+      <c r="A25" s="80"/>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
@@ -2652,7 +2652,7 @@
       <c r="E25" s="44">
         <v>13</v>
       </c>
-      <c r="I25" s="77"/>
+      <c r="I25" s="88"/>
       <c r="J25" s="5" t="s">
         <v>10</v>
       </c>
@@ -2667,7 +2667,7 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" s="83"/>
+      <c r="A26" s="80"/>
       <c r="B26" s="7" t="s">
         <v>12</v>
       </c>
@@ -2680,7 +2680,7 @@
       <c r="E26" s="43">
         <v>15</v>
       </c>
-      <c r="I26" s="77"/>
+      <c r="I26" s="88"/>
       <c r="J26" s="7" t="s">
         <v>12</v>
       </c>
@@ -2695,7 +2695,7 @@
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" s="83"/>
+      <c r="A27" s="80"/>
       <c r="B27" s="5" t="s">
         <v>14</v>
       </c>
@@ -2708,7 +2708,7 @@
       <c r="E27" s="44">
         <v>12</v>
       </c>
-      <c r="I27" s="77"/>
+      <c r="I27" s="88"/>
       <c r="J27" s="5" t="s">
         <v>14</v>
       </c>
@@ -2723,7 +2723,7 @@
       </c>
     </row>
     <row r="28" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="84"/>
+      <c r="A28" s="81"/>
       <c r="B28" s="10" t="s">
         <v>16</v>
       </c>
@@ -2736,7 +2736,7 @@
       <c r="E28" s="45">
         <v>20</v>
       </c>
-      <c r="I28" s="81"/>
+      <c r="I28" s="89"/>
       <c r="J28" s="10" t="s">
         <v>16</v>
       </c>
@@ -2751,7 +2751,7 @@
       </c>
     </row>
     <row r="29" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="83">
+      <c r="A29" s="80">
         <v>2023</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -2766,7 +2766,7 @@
       <c r="E29" s="42">
         <v>9</v>
       </c>
-      <c r="I29" s="76">
+      <c r="I29" s="87">
         <v>2023</v>
       </c>
       <c r="J29" s="3" t="s">
@@ -2783,7 +2783,7 @@
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A30" s="83"/>
+      <c r="A30" s="80"/>
       <c r="B30" s="7" t="s">
         <v>8</v>
       </c>
@@ -2796,7 +2796,7 @@
       <c r="E30" s="43">
         <v>9</v>
       </c>
-      <c r="I30" s="77"/>
+      <c r="I30" s="88"/>
       <c r="J30" s="7" t="s">
         <v>8</v>
       </c>
@@ -2811,7 +2811,7 @@
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A31" s="83"/>
+      <c r="A31" s="80"/>
       <c r="B31" s="5" t="s">
         <v>10</v>
       </c>
@@ -2824,7 +2824,7 @@
       <c r="E31" s="44">
         <v>13</v>
       </c>
-      <c r="I31" s="77"/>
+      <c r="I31" s="88"/>
       <c r="J31" s="5" t="s">
         <v>10</v>
       </c>
@@ -2839,7 +2839,7 @@
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A32" s="83"/>
+      <c r="A32" s="80"/>
       <c r="B32" s="7" t="s">
         <v>12</v>
       </c>
@@ -2852,7 +2852,7 @@
       <c r="E32" s="43">
         <v>11</v>
       </c>
-      <c r="I32" s="77"/>
+      <c r="I32" s="88"/>
       <c r="J32" s="7" t="s">
         <v>12</v>
       </c>
@@ -2867,7 +2867,7 @@
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" s="83"/>
+      <c r="A33" s="80"/>
       <c r="B33" s="5" t="s">
         <v>14</v>
       </c>
@@ -2880,7 +2880,7 @@
       <c r="E33" s="44">
         <v>15</v>
       </c>
-      <c r="I33" s="77"/>
+      <c r="I33" s="88"/>
       <c r="J33" s="5" t="s">
         <v>14</v>
       </c>
@@ -2895,7 +2895,7 @@
       </c>
     </row>
     <row r="34" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="84"/>
+      <c r="A34" s="81"/>
       <c r="B34" s="18" t="s">
         <v>16</v>
       </c>
@@ -2908,7 +2908,7 @@
       <c r="E34" s="46">
         <v>11</v>
       </c>
-      <c r="I34" s="81"/>
+      <c r="I34" s="89"/>
       <c r="J34" s="18" t="s">
         <v>16</v>
       </c>
@@ -2923,7 +2923,7 @@
       </c>
     </row>
     <row r="35" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="73">
+      <c r="A35" s="82">
         <v>2024</v>
       </c>
       <c r="B35" s="40" t="s">
@@ -2938,7 +2938,7 @@
       <c r="E35" s="37">
         <v>20</v>
       </c>
-      <c r="I35" s="76">
+      <c r="I35" s="87">
         <v>2024</v>
       </c>
       <c r="J35" s="27" t="s">
@@ -2955,7 +2955,7 @@
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="74"/>
+      <c r="A36" s="83"/>
       <c r="B36" s="23" t="s">
         <v>8</v>
       </c>
@@ -2968,7 +2968,7 @@
       <c r="E36" s="38">
         <v>15</v>
       </c>
-      <c r="I36" s="77"/>
+      <c r="I36" s="88"/>
       <c r="J36" s="20" t="s">
         <v>8</v>
       </c>
@@ -2983,7 +2983,7 @@
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37" s="74"/>
+      <c r="A37" s="83"/>
       <c r="B37" s="22" t="s">
         <v>10</v>
       </c>
@@ -2996,7 +2996,7 @@
       <c r="E37" s="38">
         <v>15</v>
       </c>
-      <c r="I37" s="77"/>
+      <c r="I37" s="88"/>
       <c r="J37" s="21" t="s">
         <v>10</v>
       </c>
@@ -3011,7 +3011,7 @@
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38" s="74"/>
+      <c r="A38" s="83"/>
       <c r="B38" s="23" t="s">
         <v>12</v>
       </c>
@@ -3024,7 +3024,7 @@
       <c r="E38" s="38">
         <v>20</v>
       </c>
-      <c r="I38" s="77"/>
+      <c r="I38" s="88"/>
       <c r="J38" s="20" t="s">
         <v>12</v>
       </c>
@@ -3039,7 +3039,7 @@
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A39" s="74"/>
+      <c r="A39" s="83"/>
       <c r="B39" s="22" t="s">
         <v>14</v>
       </c>
@@ -3052,7 +3052,7 @@
       <c r="E39" s="38">
         <v>16</v>
       </c>
-      <c r="I39" s="77"/>
+      <c r="I39" s="88"/>
       <c r="J39" s="21" t="s">
         <v>14</v>
       </c>
@@ -3067,7 +3067,7 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="75"/>
+      <c r="A40" s="84"/>
       <c r="B40" s="41" t="s">
         <v>16</v>
       </c>
@@ -3080,7 +3080,7 @@
       <c r="E40" s="39">
         <v>16</v>
       </c>
-      <c r="I40" s="78"/>
+      <c r="I40" s="99"/>
       <c r="J40" s="28" t="s">
         <v>16</v>
       </c>
@@ -3095,7 +3095,7 @@
       </c>
     </row>
     <row r="41" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="73">
+      <c r="A41" s="82">
         <v>2025</v>
       </c>
       <c r="B41" s="40" t="s">
@@ -3110,7 +3110,7 @@
       <c r="E41" s="37">
         <v>14</v>
       </c>
-      <c r="I41" s="73">
+      <c r="I41" s="82">
         <v>2025</v>
       </c>
       <c r="J41" s="40" t="s">
@@ -3127,7 +3127,7 @@
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42" s="74"/>
+      <c r="A42" s="83"/>
       <c r="B42" s="23" t="s">
         <v>8</v>
       </c>
@@ -3140,7 +3140,7 @@
       <c r="E42" s="38">
         <v>20</v>
       </c>
-      <c r="I42" s="74"/>
+      <c r="I42" s="83"/>
       <c r="J42" s="23" t="s">
         <v>8</v>
       </c>
@@ -3155,7 +3155,7 @@
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="74"/>
+      <c r="A43" s="83"/>
       <c r="B43" s="22" t="s">
         <v>10</v>
       </c>
@@ -3168,7 +3168,7 @@
       <c r="E43" s="38">
         <v>15</v>
       </c>
-      <c r="I43" s="74"/>
+      <c r="I43" s="83"/>
       <c r="J43" s="22" t="s">
         <v>10</v>
       </c>
@@ -3183,7 +3183,7 @@
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="74"/>
+      <c r="A44" s="83"/>
       <c r="B44" s="23" t="s">
         <v>12</v>
       </c>
@@ -3196,7 +3196,7 @@
       <c r="E44" s="38">
         <v>10</v>
       </c>
-      <c r="I44" s="74"/>
+      <c r="I44" s="83"/>
       <c r="J44" s="23" t="s">
         <v>12</v>
       </c>
@@ -3211,7 +3211,7 @@
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" s="74"/>
+      <c r="A45" s="83"/>
       <c r="B45" s="22" t="s">
         <v>14</v>
       </c>
@@ -3224,7 +3224,7 @@
       <c r="E45" s="38">
         <v>13</v>
       </c>
-      <c r="I45" s="74"/>
+      <c r="I45" s="83"/>
       <c r="J45" s="22" t="s">
         <v>14</v>
       </c>
@@ -3239,7 +3239,7 @@
       </c>
     </row>
     <row r="46" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="75"/>
+      <c r="A46" s="84"/>
       <c r="B46" s="41" t="s">
         <v>16</v>
       </c>
@@ -3252,7 +3252,7 @@
       <c r="E46" s="39">
         <v>16</v>
       </c>
-      <c r="I46" s="75"/>
+      <c r="I46" s="84"/>
       <c r="J46" s="41" t="s">
         <v>16</v>
       </c>
@@ -3267,7 +3267,7 @@
       </c>
     </row>
     <row r="47" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="86">
+      <c r="A47" s="79">
         <v>2026</v>
       </c>
       <c r="B47" s="40" t="s">
@@ -3280,9 +3280,9 @@
         <v>7</v>
       </c>
       <c r="E47" s="37">
-        <v>0</v>
-      </c>
-      <c r="I47" s="73">
+        <v>12</v>
+      </c>
+      <c r="I47" s="82">
         <v>2026</v>
       </c>
       <c r="J47" s="40" t="s">
@@ -3295,11 +3295,11 @@
         <v>7</v>
       </c>
       <c r="M47" s="37">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="83"/>
+      <c r="A48" s="80"/>
       <c r="B48" s="23" t="s">
         <v>8</v>
       </c>
@@ -3310,9 +3310,9 @@
         <v>9</v>
       </c>
       <c r="E48" s="38">
-        <v>0</v>
-      </c>
-      <c r="I48" s="74"/>
+        <v>14</v>
+      </c>
+      <c r="I48" s="83"/>
       <c r="J48" s="23" t="s">
         <v>8</v>
       </c>
@@ -3323,11 +3323,11 @@
         <v>9</v>
       </c>
       <c r="M48" s="38">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A49" s="83"/>
+      <c r="A49" s="80"/>
       <c r="B49" s="22" t="s">
         <v>10</v>
       </c>
@@ -3340,7 +3340,7 @@
       <c r="E49" s="38">
         <v>0</v>
       </c>
-      <c r="I49" s="74"/>
+      <c r="I49" s="83"/>
       <c r="J49" s="22" t="s">
         <v>10</v>
       </c>
@@ -3355,7 +3355,7 @@
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A50" s="83"/>
+      <c r="A50" s="80"/>
       <c r="B50" s="23" t="s">
         <v>12</v>
       </c>
@@ -3368,7 +3368,7 @@
       <c r="E50" s="38">
         <v>0</v>
       </c>
-      <c r="I50" s="74"/>
+      <c r="I50" s="83"/>
       <c r="J50" s="23" t="s">
         <v>12</v>
       </c>
@@ -3383,7 +3383,7 @@
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A51" s="83"/>
+      <c r="A51" s="80"/>
       <c r="B51" s="22" t="s">
         <v>14</v>
       </c>
@@ -3396,7 +3396,7 @@
       <c r="E51" s="38">
         <v>0</v>
       </c>
-      <c r="I51" s="74"/>
+      <c r="I51" s="83"/>
       <c r="J51" s="22" t="s">
         <v>14</v>
       </c>
@@ -3411,12 +3411,12 @@
       </c>
     </row>
     <row r="52" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="84"/>
+      <c r="A52" s="81"/>
       <c r="B52" s="41" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="29">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D52" s="30" t="s">
         <v>17</v>
@@ -3424,7 +3424,7 @@
       <c r="E52" s="39">
         <v>0</v>
       </c>
-      <c r="I52" s="75"/>
+      <c r="I52" s="84"/>
       <c r="J52" s="41" t="s">
         <v>16</v>
       </c>
@@ -3440,21 +3440,21 @@
     </row>
     <row r="53" spans="1:13" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="54" spans="1:13" ht="31.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="94" t="s">
+      <c r="A54" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="B54" s="99" t="s">
+      <c r="B54" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="I54" s="97" t="s">
+      <c r="I54" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="J54" s="98" t="s">
+      <c r="J54" s="77" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A55" s="93">
+      <c r="A55" s="72">
         <v>2019</v>
       </c>
       <c r="B55" s="62">
@@ -3468,7 +3468,7 @@
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A56" s="91">
+      <c r="A56" s="70">
         <v>2020</v>
       </c>
       <c r="B56" s="8">
@@ -3482,7 +3482,7 @@
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A57" s="91">
+      <c r="A57" s="70">
         <v>2021</v>
       </c>
       <c r="B57" s="8">
@@ -3496,7 +3496,7 @@
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A58" s="91">
+      <c r="A58" s="70">
         <v>2022</v>
       </c>
       <c r="B58" s="8">
@@ -3510,7 +3510,7 @@
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A59" s="91">
+      <c r="A59" s="70">
         <v>2023</v>
       </c>
       <c r="B59" s="8">
@@ -3524,7 +3524,7 @@
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A60" s="91">
+      <c r="A60" s="70">
         <v>2024</v>
       </c>
       <c r="B60" s="8">
@@ -3538,7 +3538,7 @@
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A61" s="91">
+      <c r="A61" s="70">
         <v>2025</v>
       </c>
       <c r="B61" s="8">
@@ -3552,37 +3552,40 @@
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A62" s="92">
+      <c r="A62" s="71">
         <v>2026</v>
       </c>
       <c r="B62" s="8">
-        <v>64</v>
-      </c>
-      <c r="I62" s="96">
+        <v>102</v>
+      </c>
+      <c r="I62" s="75">
         <v>2026</v>
       </c>
-      <c r="J62" s="96">
-        <v>25</v>
+      <c r="J62" s="75">
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A63" s="92" t="s">
+      <c r="A63" s="71" t="s">
         <v>20</v>
       </c>
       <c r="B63" s="8">
         <f>SUM(B55:B62)</f>
-        <v>1163</v>
-      </c>
-      <c r="I63" s="95" t="s">
+        <v>1201</v>
+      </c>
+      <c r="I63" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="J63" s="95">
+      <c r="J63" s="74">
         <f>SUM(J55:J62)</f>
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="I41:I46"/>
+    <mergeCell ref="A35:A40"/>
+    <mergeCell ref="I35:I40"/>
     <mergeCell ref="A47:A52"/>
     <mergeCell ref="I47:I52"/>
     <mergeCell ref="A1:M1"/>
@@ -3599,9 +3602,6 @@
     <mergeCell ref="I5:I10"/>
     <mergeCell ref="I11:I16"/>
     <mergeCell ref="A41:A46"/>
-    <mergeCell ref="I41:I46"/>
-    <mergeCell ref="A35:A40"/>
-    <mergeCell ref="I35:I40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
@@ -3709,10 +3709,10 @@
         <v>2026</v>
       </c>
       <c r="B9" s="67">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="C9" s="50">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -3847,10 +3847,10 @@
         <v>2026</v>
       </c>
       <c r="B9">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C9">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -3961,7 +3961,7 @@
         <v>2026</v>
       </c>
       <c r="B7">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -4026,7 +4026,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -4072,7 +4072,7 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -4095,7 +4095,7 @@
         <v>39</v>
       </c>
       <c r="G5">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4118,7 +4118,7 @@
         <v>17</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -4141,7 +4141,7 @@
         <v>17</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -4164,7 +4164,7 @@
         <v>9</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -4233,7 +4233,7 @@
         <v>6</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -4256,7 +4256,7 @@
         <v>19</v>
       </c>
       <c r="G12">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -4279,7 +4279,7 @@
         <v>44</v>
       </c>
       <c r="G13">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="G15" s="69">
         <f>SUM(G2:G14)</f>
-        <v>75</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/data/Prevencion_de_violencia_de_genero_CAVV/SAFEkits.xlsx
+++ b/data/Prevencion_de_violencia_de_genero_CAVV/SAFEkits.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Prevencion_de_violencia_de_genero_CAVV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F7677C-40B5-4B35-BC20-A0BF885B6800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53BD4B40-E515-40DA-969C-753C0C099821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9984" yWindow="1164" windowWidth="11424" windowHeight="9420" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9744" yWindow="1728" windowWidth="12564" windowHeight="9384" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen" sheetId="1" r:id="rId1"/>
@@ -1344,6 +1344,24 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1353,26 +1371,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1402,9 +1405,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1998,37 +1998,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="85"/>
-      <c r="M1" s="85"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
     </row>
     <row r="3" spans="1:13" ht="21" x14ac:dyDescent="0.4">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="I3" s="86" t="s">
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="I3" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="86"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
     </row>
     <row r="4" spans="1:13" ht="31.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="24" t="s">
@@ -2063,7 +2063,7 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="93">
+      <c r="A5" s="94">
         <v>2019</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -2078,7 +2078,7 @@
       <c r="E5" s="3">
         <v>14</v>
       </c>
-      <c r="I5" s="96">
+      <c r="I5" s="97">
         <v>2019</v>
       </c>
       <c r="J5" s="3" t="s">
@@ -2095,7 +2095,7 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="94"/>
+      <c r="A6" s="95"/>
       <c r="B6" s="7" t="s">
         <v>8</v>
       </c>
@@ -2108,7 +2108,7 @@
       <c r="E6" s="7">
         <v>13</v>
       </c>
-      <c r="I6" s="97"/>
+      <c r="I6" s="98"/>
       <c r="J6" s="7" t="s">
         <v>8</v>
       </c>
@@ -2123,7 +2123,7 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="94"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="5" t="s">
         <v>10</v>
       </c>
@@ -2136,7 +2136,7 @@
       <c r="E7" s="5">
         <v>10</v>
       </c>
-      <c r="I7" s="97"/>
+      <c r="I7" s="98"/>
       <c r="J7" s="5" t="s">
         <v>10</v>
       </c>
@@ -2151,7 +2151,7 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="94"/>
+      <c r="A8" s="95"/>
       <c r="B8" s="7" t="s">
         <v>12</v>
       </c>
@@ -2164,7 +2164,7 @@
       <c r="E8" s="7">
         <v>9</v>
       </c>
-      <c r="I8" s="97"/>
+      <c r="I8" s="98"/>
       <c r="J8" s="7" t="s">
         <v>12</v>
       </c>
@@ -2179,7 +2179,7 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="94"/>
+      <c r="A9" s="95"/>
       <c r="B9" s="5" t="s">
         <v>14</v>
       </c>
@@ -2192,7 +2192,7 @@
       <c r="E9" s="5">
         <v>11</v>
       </c>
-      <c r="I9" s="97"/>
+      <c r="I9" s="98"/>
       <c r="J9" s="5" t="s">
         <v>14</v>
       </c>
@@ -2207,7 +2207,7 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="95"/>
+      <c r="A10" s="96"/>
       <c r="B10" s="10" t="s">
         <v>16</v>
       </c>
@@ -2220,7 +2220,7 @@
       <c r="E10" s="10">
         <v>14</v>
       </c>
-      <c r="I10" s="98"/>
+      <c r="I10" s="99"/>
       <c r="J10" s="10" t="s">
         <v>16</v>
       </c>
@@ -2235,7 +2235,7 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="93">
+      <c r="A11" s="94">
         <v>2020</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -2250,7 +2250,7 @@
       <c r="E11" s="3">
         <v>5</v>
       </c>
-      <c r="I11" s="96">
+      <c r="I11" s="97">
         <v>2020</v>
       </c>
       <c r="J11" s="61" t="s">
@@ -2267,7 +2267,7 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="94"/>
+      <c r="A12" s="95"/>
       <c r="B12" s="7" t="s">
         <v>8</v>
       </c>
@@ -2280,7 +2280,7 @@
       <c r="E12" s="7">
         <v>13</v>
       </c>
-      <c r="I12" s="97"/>
+      <c r="I12" s="98"/>
       <c r="J12" s="7" t="s">
         <v>8</v>
       </c>
@@ -2295,7 +2295,7 @@
       </c>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="94"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
@@ -2308,7 +2308,7 @@
       <c r="E13" s="5">
         <v>14</v>
       </c>
-      <c r="I13" s="97"/>
+      <c r="I13" s="98"/>
       <c r="J13" s="5" t="s">
         <v>10</v>
       </c>
@@ -2323,7 +2323,7 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="94"/>
+      <c r="A14" s="95"/>
       <c r="B14" s="7" t="s">
         <v>12</v>
       </c>
@@ -2336,7 +2336,7 @@
       <c r="E14" s="7">
         <v>19</v>
       </c>
-      <c r="I14" s="97"/>
+      <c r="I14" s="98"/>
       <c r="J14" s="7" t="s">
         <v>12</v>
       </c>
@@ -2351,7 +2351,7 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="94"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="5" t="s">
         <v>14</v>
       </c>
@@ -2364,7 +2364,7 @@
       <c r="E15" s="5">
         <v>9</v>
       </c>
-      <c r="I15" s="97"/>
+      <c r="I15" s="98"/>
       <c r="J15" s="5" t="s">
         <v>14</v>
       </c>
@@ -2379,7 +2379,7 @@
       </c>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="95"/>
+      <c r="A16" s="96"/>
       <c r="B16" s="10" t="s">
         <v>16</v>
       </c>
@@ -2392,7 +2392,7 @@
       <c r="E16" s="10">
         <v>9</v>
       </c>
-      <c r="I16" s="98"/>
+      <c r="I16" s="99"/>
       <c r="J16" s="10" t="s">
         <v>16</v>
       </c>
@@ -2407,7 +2407,7 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="79">
+      <c r="A17" s="85">
         <v>2021</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -2422,7 +2422,7 @@
       <c r="E17" s="42">
         <v>15</v>
       </c>
-      <c r="I17" s="90">
+      <c r="I17" s="91">
         <v>2021</v>
       </c>
       <c r="J17" s="3" t="s">
@@ -2439,7 +2439,7 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="80"/>
+      <c r="A18" s="86"/>
       <c r="B18" s="7" t="s">
         <v>8</v>
       </c>
@@ -2452,7 +2452,7 @@
       <c r="E18" s="43">
         <v>13</v>
       </c>
-      <c r="I18" s="88"/>
+      <c r="I18" s="83"/>
       <c r="J18" s="7" t="s">
         <v>8</v>
       </c>
@@ -2467,7 +2467,7 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="80"/>
+      <c r="A19" s="86"/>
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
@@ -2480,7 +2480,7 @@
       <c r="E19" s="44">
         <v>7</v>
       </c>
-      <c r="I19" s="88"/>
+      <c r="I19" s="83"/>
       <c r="J19" s="5" t="s">
         <v>10</v>
       </c>
@@ -2495,7 +2495,7 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="80"/>
+      <c r="A20" s="86"/>
       <c r="B20" s="7" t="s">
         <v>12</v>
       </c>
@@ -2508,7 +2508,7 @@
       <c r="E20" s="43">
         <v>9</v>
       </c>
-      <c r="I20" s="88"/>
+      <c r="I20" s="83"/>
       <c r="J20" s="7" t="s">
         <v>12</v>
       </c>
@@ -2523,7 +2523,7 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="80"/>
+      <c r="A21" s="86"/>
       <c r="B21" s="5" t="s">
         <v>14</v>
       </c>
@@ -2536,7 +2536,7 @@
       <c r="E21" s="44">
         <v>10</v>
       </c>
-      <c r="I21" s="88"/>
+      <c r="I21" s="83"/>
       <c r="J21" s="5" t="s">
         <v>14</v>
       </c>
@@ -2551,7 +2551,7 @@
       </c>
     </row>
     <row r="22" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="92"/>
+      <c r="A22" s="93"/>
       <c r="B22" s="10" t="s">
         <v>16</v>
       </c>
@@ -2564,7 +2564,7 @@
       <c r="E22" s="45">
         <v>8</v>
       </c>
-      <c r="I22" s="89"/>
+      <c r="I22" s="90"/>
       <c r="J22" s="10" t="s">
         <v>16</v>
       </c>
@@ -2579,7 +2579,7 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="91">
+      <c r="A23" s="92">
         <v>2022</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -2594,7 +2594,7 @@
       <c r="E23" s="42">
         <v>7</v>
       </c>
-      <c r="I23" s="87">
+      <c r="I23" s="82">
         <v>2022</v>
       </c>
       <c r="J23" s="3" t="s">
@@ -2611,7 +2611,7 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="80"/>
+      <c r="A24" s="86"/>
       <c r="B24" s="7" t="s">
         <v>8</v>
       </c>
@@ -2624,7 +2624,7 @@
       <c r="E24" s="43">
         <v>17</v>
       </c>
-      <c r="I24" s="88"/>
+      <c r="I24" s="83"/>
       <c r="J24" s="7" t="s">
         <v>8</v>
       </c>
@@ -2639,7 +2639,7 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" s="80"/>
+      <c r="A25" s="86"/>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
@@ -2652,7 +2652,7 @@
       <c r="E25" s="44">
         <v>13</v>
       </c>
-      <c r="I25" s="88"/>
+      <c r="I25" s="83"/>
       <c r="J25" s="5" t="s">
         <v>10</v>
       </c>
@@ -2667,7 +2667,7 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" s="80"/>
+      <c r="A26" s="86"/>
       <c r="B26" s="7" t="s">
         <v>12</v>
       </c>
@@ -2680,7 +2680,7 @@
       <c r="E26" s="43">
         <v>15</v>
       </c>
-      <c r="I26" s="88"/>
+      <c r="I26" s="83"/>
       <c r="J26" s="7" t="s">
         <v>12</v>
       </c>
@@ -2695,7 +2695,7 @@
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" s="80"/>
+      <c r="A27" s="86"/>
       <c r="B27" s="5" t="s">
         <v>14</v>
       </c>
@@ -2708,7 +2708,7 @@
       <c r="E27" s="44">
         <v>12</v>
       </c>
-      <c r="I27" s="88"/>
+      <c r="I27" s="83"/>
       <c r="J27" s="5" t="s">
         <v>14</v>
       </c>
@@ -2723,7 +2723,7 @@
       </c>
     </row>
     <row r="28" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="81"/>
+      <c r="A28" s="87"/>
       <c r="B28" s="10" t="s">
         <v>16</v>
       </c>
@@ -2736,7 +2736,7 @@
       <c r="E28" s="45">
         <v>20</v>
       </c>
-      <c r="I28" s="89"/>
+      <c r="I28" s="90"/>
       <c r="J28" s="10" t="s">
         <v>16</v>
       </c>
@@ -2751,7 +2751,7 @@
       </c>
     </row>
     <row r="29" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="80">
+      <c r="A29" s="86">
         <v>2023</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -2766,7 +2766,7 @@
       <c r="E29" s="42">
         <v>9</v>
       </c>
-      <c r="I29" s="87">
+      <c r="I29" s="82">
         <v>2023</v>
       </c>
       <c r="J29" s="3" t="s">
@@ -2783,7 +2783,7 @@
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A30" s="80"/>
+      <c r="A30" s="86"/>
       <c r="B30" s="7" t="s">
         <v>8</v>
       </c>
@@ -2796,7 +2796,7 @@
       <c r="E30" s="43">
         <v>9</v>
       </c>
-      <c r="I30" s="88"/>
+      <c r="I30" s="83"/>
       <c r="J30" s="7" t="s">
         <v>8</v>
       </c>
@@ -2811,7 +2811,7 @@
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A31" s="80"/>
+      <c r="A31" s="86"/>
       <c r="B31" s="5" t="s">
         <v>10</v>
       </c>
@@ -2824,7 +2824,7 @@
       <c r="E31" s="44">
         <v>13</v>
       </c>
-      <c r="I31" s="88"/>
+      <c r="I31" s="83"/>
       <c r="J31" s="5" t="s">
         <v>10</v>
       </c>
@@ -2839,7 +2839,7 @@
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A32" s="80"/>
+      <c r="A32" s="86"/>
       <c r="B32" s="7" t="s">
         <v>12</v>
       </c>
@@ -2852,7 +2852,7 @@
       <c r="E32" s="43">
         <v>11</v>
       </c>
-      <c r="I32" s="88"/>
+      <c r="I32" s="83"/>
       <c r="J32" s="7" t="s">
         <v>12</v>
       </c>
@@ -2867,7 +2867,7 @@
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" s="80"/>
+      <c r="A33" s="86"/>
       <c r="B33" s="5" t="s">
         <v>14</v>
       </c>
@@ -2880,7 +2880,7 @@
       <c r="E33" s="44">
         <v>15</v>
       </c>
-      <c r="I33" s="88"/>
+      <c r="I33" s="83"/>
       <c r="J33" s="5" t="s">
         <v>14</v>
       </c>
@@ -2895,7 +2895,7 @@
       </c>
     </row>
     <row r="34" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="81"/>
+      <c r="A34" s="87"/>
       <c r="B34" s="18" t="s">
         <v>16</v>
       </c>
@@ -2908,7 +2908,7 @@
       <c r="E34" s="46">
         <v>11</v>
       </c>
-      <c r="I34" s="89"/>
+      <c r="I34" s="90"/>
       <c r="J34" s="18" t="s">
         <v>16</v>
       </c>
@@ -2923,7 +2923,7 @@
       </c>
     </row>
     <row r="35" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="82">
+      <c r="A35" s="79">
         <v>2024</v>
       </c>
       <c r="B35" s="40" t="s">
@@ -2938,7 +2938,7 @@
       <c r="E35" s="37">
         <v>20</v>
       </c>
-      <c r="I35" s="87">
+      <c r="I35" s="82">
         <v>2024</v>
       </c>
       <c r="J35" s="27" t="s">
@@ -2955,7 +2955,7 @@
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="83"/>
+      <c r="A36" s="80"/>
       <c r="B36" s="23" t="s">
         <v>8</v>
       </c>
@@ -2968,7 +2968,7 @@
       <c r="E36" s="38">
         <v>15</v>
       </c>
-      <c r="I36" s="88"/>
+      <c r="I36" s="83"/>
       <c r="J36" s="20" t="s">
         <v>8</v>
       </c>
@@ -2983,7 +2983,7 @@
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37" s="83"/>
+      <c r="A37" s="80"/>
       <c r="B37" s="22" t="s">
         <v>10</v>
       </c>
@@ -2996,7 +2996,7 @@
       <c r="E37" s="38">
         <v>15</v>
       </c>
-      <c r="I37" s="88"/>
+      <c r="I37" s="83"/>
       <c r="J37" s="21" t="s">
         <v>10</v>
       </c>
@@ -3011,7 +3011,7 @@
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38" s="83"/>
+      <c r="A38" s="80"/>
       <c r="B38" s="23" t="s">
         <v>12</v>
       </c>
@@ -3024,7 +3024,7 @@
       <c r="E38" s="38">
         <v>20</v>
       </c>
-      <c r="I38" s="88"/>
+      <c r="I38" s="83"/>
       <c r="J38" s="20" t="s">
         <v>12</v>
       </c>
@@ -3039,7 +3039,7 @@
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A39" s="83"/>
+      <c r="A39" s="80"/>
       <c r="B39" s="22" t="s">
         <v>14</v>
       </c>
@@ -3052,7 +3052,7 @@
       <c r="E39" s="38">
         <v>16</v>
       </c>
-      <c r="I39" s="88"/>
+      <c r="I39" s="83"/>
       <c r="J39" s="21" t="s">
         <v>14</v>
       </c>
@@ -3067,7 +3067,7 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="84"/>
+      <c r="A40" s="81"/>
       <c r="B40" s="41" t="s">
         <v>16</v>
       </c>
@@ -3080,7 +3080,7 @@
       <c r="E40" s="39">
         <v>16</v>
       </c>
-      <c r="I40" s="99"/>
+      <c r="I40" s="84"/>
       <c r="J40" s="28" t="s">
         <v>16</v>
       </c>
@@ -3095,7 +3095,7 @@
       </c>
     </row>
     <row r="41" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="82">
+      <c r="A41" s="79">
         <v>2025</v>
       </c>
       <c r="B41" s="40" t="s">
@@ -3110,7 +3110,7 @@
       <c r="E41" s="37">
         <v>14</v>
       </c>
-      <c r="I41" s="82">
+      <c r="I41" s="79">
         <v>2025</v>
       </c>
       <c r="J41" s="40" t="s">
@@ -3127,7 +3127,7 @@
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42" s="83"/>
+      <c r="A42" s="80"/>
       <c r="B42" s="23" t="s">
         <v>8</v>
       </c>
@@ -3140,7 +3140,7 @@
       <c r="E42" s="38">
         <v>20</v>
       </c>
-      <c r="I42" s="83"/>
+      <c r="I42" s="80"/>
       <c r="J42" s="23" t="s">
         <v>8</v>
       </c>
@@ -3155,7 +3155,7 @@
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="83"/>
+      <c r="A43" s="80"/>
       <c r="B43" s="22" t="s">
         <v>10</v>
       </c>
@@ -3168,7 +3168,7 @@
       <c r="E43" s="38">
         <v>15</v>
       </c>
-      <c r="I43" s="83"/>
+      <c r="I43" s="80"/>
       <c r="J43" s="22" t="s">
         <v>10</v>
       </c>
@@ -3183,7 +3183,7 @@
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="83"/>
+      <c r="A44" s="80"/>
       <c r="B44" s="23" t="s">
         <v>12</v>
       </c>
@@ -3196,7 +3196,7 @@
       <c r="E44" s="38">
         <v>10</v>
       </c>
-      <c r="I44" s="83"/>
+      <c r="I44" s="80"/>
       <c r="J44" s="23" t="s">
         <v>12</v>
       </c>
@@ -3211,7 +3211,7 @@
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" s="83"/>
+      <c r="A45" s="80"/>
       <c r="B45" s="22" t="s">
         <v>14</v>
       </c>
@@ -3224,7 +3224,7 @@
       <c r="E45" s="38">
         <v>13</v>
       </c>
-      <c r="I45" s="83"/>
+      <c r="I45" s="80"/>
       <c r="J45" s="22" t="s">
         <v>14</v>
       </c>
@@ -3239,7 +3239,7 @@
       </c>
     </row>
     <row r="46" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="84"/>
+      <c r="A46" s="81"/>
       <c r="B46" s="41" t="s">
         <v>16</v>
       </c>
@@ -3252,7 +3252,7 @@
       <c r="E46" s="39">
         <v>16</v>
       </c>
-      <c r="I46" s="84"/>
+      <c r="I46" s="81"/>
       <c r="J46" s="41" t="s">
         <v>16</v>
       </c>
@@ -3267,7 +3267,7 @@
       </c>
     </row>
     <row r="47" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="79">
+      <c r="A47" s="85">
         <v>2026</v>
       </c>
       <c r="B47" s="40" t="s">
@@ -3282,7 +3282,7 @@
       <c r="E47" s="37">
         <v>12</v>
       </c>
-      <c r="I47" s="82">
+      <c r="I47" s="79">
         <v>2026</v>
       </c>
       <c r="J47" s="40" t="s">
@@ -3299,7 +3299,7 @@
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="80"/>
+      <c r="A48" s="86"/>
       <c r="B48" s="23" t="s">
         <v>8</v>
       </c>
@@ -3310,9 +3310,9 @@
         <v>9</v>
       </c>
       <c r="E48" s="38">
-        <v>14</v>
-      </c>
-      <c r="I48" s="83"/>
+        <v>15</v>
+      </c>
+      <c r="I48" s="80"/>
       <c r="J48" s="23" t="s">
         <v>8</v>
       </c>
@@ -3323,11 +3323,11 @@
         <v>9</v>
       </c>
       <c r="M48" s="38">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A49" s="80"/>
+      <c r="A49" s="86"/>
       <c r="B49" s="22" t="s">
         <v>10</v>
       </c>
@@ -3338,9 +3338,9 @@
         <v>11</v>
       </c>
       <c r="E49" s="38">
-        <v>0</v>
-      </c>
-      <c r="I49" s="83"/>
+        <v>13</v>
+      </c>
+      <c r="I49" s="80"/>
       <c r="J49" s="22" t="s">
         <v>10</v>
       </c>
@@ -3351,11 +3351,11 @@
         <v>11</v>
       </c>
       <c r="M49" s="38">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A50" s="80"/>
+      <c r="A50" s="86"/>
       <c r="B50" s="23" t="s">
         <v>12</v>
       </c>
@@ -3368,7 +3368,7 @@
       <c r="E50" s="38">
         <v>0</v>
       </c>
-      <c r="I50" s="83"/>
+      <c r="I50" s="80"/>
       <c r="J50" s="23" t="s">
         <v>12</v>
       </c>
@@ -3383,7 +3383,7 @@
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A51" s="80"/>
+      <c r="A51" s="86"/>
       <c r="B51" s="22" t="s">
         <v>14</v>
       </c>
@@ -3396,7 +3396,7 @@
       <c r="E51" s="38">
         <v>0</v>
       </c>
-      <c r="I51" s="83"/>
+      <c r="I51" s="80"/>
       <c r="J51" s="22" t="s">
         <v>14</v>
       </c>
@@ -3411,7 +3411,7 @@
       </c>
     </row>
     <row r="52" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="81"/>
+      <c r="A52" s="87"/>
       <c r="B52" s="41" t="s">
         <v>16</v>
       </c>
@@ -3424,7 +3424,7 @@
       <c r="E52" s="39">
         <v>0</v>
       </c>
-      <c r="I52" s="84"/>
+      <c r="I52" s="81"/>
       <c r="J52" s="41" t="s">
         <v>16</v>
       </c>
@@ -3556,13 +3556,13 @@
         <v>2026</v>
       </c>
       <c r="B62" s="8">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="I62" s="75">
         <v>2026</v>
       </c>
       <c r="J62" s="75">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
@@ -3571,23 +3571,18 @@
       </c>
       <c r="B63" s="8">
         <f>SUM(B55:B62)</f>
-        <v>1201</v>
+        <v>1215</v>
       </c>
       <c r="I63" s="74" t="s">
         <v>20</v>
       </c>
       <c r="J63" s="74">
         <f>SUM(J55:J62)</f>
-        <v>272</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="I41:I46"/>
-    <mergeCell ref="A35:A40"/>
-    <mergeCell ref="I35:I40"/>
-    <mergeCell ref="A47:A52"/>
-    <mergeCell ref="I47:I52"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="I3:M3"/>
@@ -3601,6 +3596,11 @@
     <mergeCell ref="A5:A10"/>
     <mergeCell ref="I5:I10"/>
     <mergeCell ref="I11:I16"/>
+    <mergeCell ref="I41:I46"/>
+    <mergeCell ref="A35:A40"/>
+    <mergeCell ref="I35:I40"/>
+    <mergeCell ref="A47:A52"/>
+    <mergeCell ref="I47:I52"/>
     <mergeCell ref="A41:A46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3709,10 +3709,10 @@
         <v>2026</v>
       </c>
       <c r="B9" s="67">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="C9" s="50">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -3847,10 +3847,10 @@
         <v>2026</v>
       </c>
       <c r="B9">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C9">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -3961,7 +3961,7 @@
         <v>2026</v>
       </c>
       <c r="B7">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -4095,7 +4095,7 @@
         <v>39</v>
       </c>
       <c r="G5">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4118,7 +4118,7 @@
         <v>17</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -4187,7 +4187,7 @@
         <v>5</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -4210,7 +4210,7 @@
         <v>6</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -4256,7 +4256,7 @@
         <v>19</v>
       </c>
       <c r="G12">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -4279,7 +4279,7 @@
         <v>44</v>
       </c>
       <c r="G13">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -4302,7 +4302,7 @@
         <v>4</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="G15" s="69">
         <f>SUM(G2:G14)</f>
-        <v>102</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
